--- a/docs/literature_review_table.xlsx
+++ b/docs/literature_review_table.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Literature Review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Literature Review'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Literature Review'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,12 +35,18 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="9">
@@ -112,33 +118,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -506,17 +518,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -552,12 +565,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Summary (1 sentence)</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Full citation</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
         </is>
       </c>
     </row>
@@ -587,17 +605,22 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>correspondence study; racial discrimination; resume audit; name-based signal; callback rate</t>
+          <t>correspondence study; racial discrimination; resume audit; name; callback rate</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Sending 5,000 matched resumes in Boston and Chicago, White-sounding names received ~50% more callbacks than Black-sounding names, with the gap stable across industries and employer sizes.</t>
+          <t>Resumes with White-sounding names received ~50% more callbacks than identical resumes with Black-sounding names across Boston and Chicago employers.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Bertrand, M., &amp; Mullainathan, S. (2004). American Economic Review, 94(4), 991–1013.</t>
+          <t>Bertrand, M., &amp; Mullainathan, S. (2004). AER, 94(4), 991–1013.</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257/0002828042002561</t>
         </is>
       </c>
     </row>
@@ -607,37 +630,42 @@
           <t>1. Correspondence studies</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Oreopoulos</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Why Do Skilled Immigrants Struggle in the Labor Market? A Field Experiment with Thirteen Thousand Resumes</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>American Economic Journal: Economic Policy</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>immigration; discrimination; name; accent; Canadian labor market; correspondence study</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>In Canada, resumes with Indian, Chinese, or Pakistani names received far fewer callbacks than identical resumes with English-sounding names, even with Canadian education and experience.</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Oreopoulos, P. (2011). American Economic Journal: Economic Policy, 3(4), 148–171.</t>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>immigration; discrimination; name; Canadian labor market; correspondence study</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>In Canada, Indian, Chinese, or Pakistani names received far fewer callbacks than English-sounding names even with Canadian credentials.</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Oreopoulos, P. (2011). AEJ: Economic Policy, 3(4), 148–171.</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257/pol.3.4.148</t>
         </is>
       </c>
     </row>
@@ -672,12 +700,17 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Resumes signaling gay identity (via a college LGBT organization) received 40% fewer callbacks than otherwise identical resumes in more conservative US regions.</t>
+          <t>Resumes signaling gay identity received 40% fewer callbacks than identical resumes in more conservative US regions.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Tilcsik, A. (2011). American Journal of Sociology, 117(2), 586–626.</t>
+          <t>Tilcsik, A. (2011). AJS, 117(2), 586–626.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1086/661903</t>
         </is>
       </c>
     </row>
@@ -687,37 +720,42 @@
           <t>1. Correspondence studies</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Correll, Benard &amp; Paik</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>2007</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Getting a Job: Is There a Motherhood Penalty?</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>American Journal of Sociology</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>gender; motherhood; correspondence study; audit; hiring penalty</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Mothers were rated less competent and less committed, offered lower salaries, and held to higher performance standards than childless women with identical resumes.</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Correll, S. J., Benard, S., &amp; Paik, I. (2007). American Journal of Sociology, 112(5), 1297–1338.</t>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>gender; motherhood; correspondence study; hiring penalty; competence</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Mothers were rated less competent, offered lower salaries, and held to higher performance standards than childless women with identical resumes.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Correll, S. J., Benard, S., &amp; Paik, I. (2007). AJS, 112(5), 1297–1338.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1086/511799</t>
         </is>
       </c>
     </row>
@@ -752,12 +790,17 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Older job applicants (especially women) received significantly fewer callbacks than younger applicants with otherwise identical resumes across a range of low-skill occupations.</t>
+          <t>Older applicants, especially women, received significantly fewer callbacks than younger applicants with identical resumes across low-skill occupations.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Neumark, D., Burn, I., &amp; Button, P. (2019). Journal of Political Economy, 127(2), 922–970.</t>
+          <t>Neumark, D., Burn, I., &amp; Button, P. (2019). JPE, 127(2), 922–970.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1086/701899</t>
         </is>
       </c>
     </row>
@@ -767,37 +810,42 @@
           <t>1. Correspondence studies</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Ameri et al.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>The Disability Employment Puzzle: A Field Experiment on Employer Hiring Behavior</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>ILR Review</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>disability; employment; discrimination; resume audit; callback</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Applicants who disclosed a disability (spinal cord injury or Asperger's) received about 26% fewer interview requests than identical non-disclosing applicants.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Ameri, M., Schur, L., Adya, M., Bentley, F. S., McKay, P., &amp; Kruse, D. (2018). ILR Review, 71(2), 329–364.</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Applicants disclosing a disability received about 26% fewer interview requests than non-disclosing applicants with otherwise identical resumes.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Ameri, M. et al. (2018). ILR Review, 71(2), 329–364.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/0019793917717474</t>
         </is>
       </c>
     </row>
@@ -827,62 +875,72 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>warmth; competence; callback rate; meta-analysis; stereotype content model; labor market; correspondence study</t>
+          <t>warmth; competence; callback rate; meta-analysis; SCM; labor market; correspondence study; benchmark</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Across a decade of North American correspondence studies covering race, gender, disability, religion and more, human warmth and competence ratings of social signals predict callback disparities with r²≈0.70.</t>
+          <t>Human warmth and competence ratings of social signals predict callback disparities (r2 ~0.70) across two decades of North American correspondence studies. KEY BENCHMARK for this paper.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Gallo, E., Hausladen, C. I., Hsu, M., Jenkins, A., Ona, D., &amp; Camerer, C. (2024). PLOS ONE, 19(7): e0304723.</t>
+          <t>Gallo, E., Hausladen, C. I. et al. (2024). PLOS ONE, 19(7): e0304723.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC11236140/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2. Stereotype Content Model</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Fiske, Cuddy, Glick &amp; Xu</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>2002</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>A Model of (Often Mixed) Stereotype Content: Competence and Warmth Respectively Follow from Perceived Status and Competition</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Journal of Personality and Social Psychology</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>stereotype content model; warmth; competence; social perception; ambivalent stereotypes; status; competition</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Introduces the SCM: social groups are perceived along warmth (intentions) and competence (ability) dimensions, with status predicting competence and competition predicting (low) warmth.</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Fiske, S. T., Cuddy, A. J. C., Glick, P., &amp; Xu, J. (2002). Journal of Personality and Social Psychology, 82(6), 878–902.</t>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>stereotype content model; warmth; competence; social perception; ambivalent stereotypes; status; SCM</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Introduces the SCM: social groups are perceived along warmth (intentions) and competence (ability) dimensions; status predicts competence, competition predicts (low) warmth.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Fiske, S. T. et al. (2002). JPSP, 82(6), 878–902.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1037/0022-3514.82.6.878</t>
         </is>
       </c>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>2. Stereotype Content Model</t>
         </is>
@@ -912,57 +970,67 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Reviews cross-cultural evidence that warmth and competence are universal primary dimensions of social perception, with warmth being judged first and weighted more heavily.</t>
+          <t>Reviews cross-cultural evidence that warmth and competence are universal primary dimensions of social perception, with warmth judged first and weighted more heavily.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Fiske, S. T., Cuddy, A. J. C., &amp; Glick, P. (2007). Trends in Cognitive Sciences, 11(2), 77–83.</t>
+          <t>Fiske, S. T. et al. (2007). Trends in Cognitive Sciences, 11(2), 77–83.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.tics.2006.11.005</t>
         </is>
       </c>
     </row>
     <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>2. Stereotype Content Model</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Cuddy, Fiske &amp; Glick</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>2007</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>The BIAS Map: Behaviors from Intergroup Affect and Stereotypes</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Journal of Personality and Social Psychology</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>BIAS map; warmth; competence; intergroup behavior; discrimination; active harm; passive facilitation</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Extends SCM to behavioral predictions: groups perceived as low-warmth/low-competence elicit active harm; high-warmth/high-competence elicit active facilitation.</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Cuddy, A. J. C., Fiske, S. T., &amp; Glick, P. (2007). Journal of Personality and Social Psychology, 92(4), 631–648.</t>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>BIAS map; warmth; competence; intergroup behavior; discrimination; active harm</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Extends SCM to behavioral predictions: low-warmth/low-competence groups elicit active harm; high-warmth/high-competence groups elicit active facilitation.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Cuddy, A. J. C. et al. (2007). JPSP, 92(4), 631–648.</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1037/0022-3514.92.4.631</t>
         </is>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>2. Stereotype Content Model</t>
         </is>
@@ -992,57 +1060,67 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Comprehensive review synthesizing SCM and BIAS Map: warmth judgments come first, predict affect (pity, envy, pride, contempt), and those in turn predict discriminatory behaviors.</t>
+          <t>Comprehensive review synthesizing SCM and BIAS Map; warmth judgments come first, predict affect (pity/envy/pride/contempt), and those predict discriminatory behaviors.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Cuddy, A. J. C., Fiske, S. T., &amp; Glick, P. (2008). Advances in Experimental Social Psychology, 40, 61–149.</t>
+          <t>Cuddy, A. J. C. et al. (2008). Adv. Exp. Soc. Psych., 40, 61–149.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/S0065-2601(07)00002-0</t>
         </is>
       </c>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>2. Stereotype Content Model</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Fiske</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Stereotype Content: Warmth and Competence Endure</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Current Directions in Psychological Science</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>warmth; competence; stereotype; SCM; review; endurance; cross-cultural</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Brief review confirming that the warmth/competence structure of social perception has replicated across dozens of cultures and many decades of research.</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Fiske, S. T. (2018). Current Directions in Psychological Science, 27(2), 67–73.</t>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>warmth; competence; stereotype; SCM; review; cross-cultural</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Brief review confirming the warmth/competence structure has replicated across dozens of cultures and decades.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Fiske, S. T. (2018). Curr. Dir. Psych. Science, 27(2), 67–73.</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/0963721417738825</t>
         </is>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>3. LLM bias in hiring</t>
         </is>
@@ -1072,57 +1150,67 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Large-scale audit of GPT-3.5 across 300 names and 41 occupations finds systematic disparities; Hispanic-associated names show below-average acceptance rates in several job categories.</t>
+          <t>Large-scale audit of GPT-3.5 across 300 names and 41 occupations finds systematic disparities; Hispanic-associated names show below-average acceptance rates.</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Armstrong, R. E., Deng, M., Perez, E., &amp; Li, J. (2024). arXiv:2406.10486.</t>
+          <t>Armstrong, R. E. et al. (2024). arXiv:2406.10486.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2406.10486</t>
         </is>
       </c>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>3. LLM bias in hiring</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Gaebler, Goel, Huq &amp; Tambe</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Auditing Large Language Models for Race and Gender Disparities: Implications for AI-Based Hiring</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Socius / Sage Journals</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Socius</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>LLM; hiring bias; audit; race; gender; disparate impact; EEO law</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Audits multiple LLMs for race and gender disparities in hiring recommendations, finding persistent and legally concerning disparities that vary in direction and magnitude across models.</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Gaebler, J. D., Goel, S., Huq, A., &amp; Tambe, P. (2024). Socius. https://doi.org/10.1177/23794607251320229</t>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Audits multiple LLMs for race and gender disparities in hiring recommendations; finds persistent and legally concerning disparities that vary across models.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Gaebler, J. D. et al. (2024). Socius. doi:10.1177/23794607251320229</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/doi/10.1177/23794607251320229</t>
         </is>
       </c>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>4. Mechanistic interpretability</t>
         </is>
@@ -1152,57 +1240,67 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Introduces Word2Vec and demonstrates that semantic relationships (king − man + woman ≈ queen) are encoded as linear directions in the embedding space — the empirical seed of the linear representation hypothesis.</t>
+          <t>Introduces Word2Vec and demonstrates that semantic relationships (king - man + woman = queen) are encoded as linear directions in embedding space. Empirical seed of the linear representation hypothesis.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Mikolov, T., Chen, K., Corrado, G., &amp; Dean, J. (2013). arXiv:1301.3781.</t>
+          <t>Mikolov, T. et al. (2013). arXiv:1301.3781.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1301.3781</t>
         </is>
       </c>
     </row>
     <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>4. Mechanistic interpretability</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Olah et al.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Zoom In: An Introduction to Circuits</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Distill</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>circuits; mechanistic interpretability; features; neural networks; vision; polysemanticity</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>circuits; mechanistic interpretability; features; neural networks; polysemanticity</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Introduces the circuits framework for mechanistic interpretability: neural networks can be understood by identifying interpretable features and the circuits that compose them.</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Olah, C., Cammarata, N., Schubert, L., Goh, G., Petrov, M., &amp; Carter, S. (2020). Distill. https://distill.pub/2020/circuits/zoom-in</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Olah, C. et al. (2020). Distill.</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>https://distill.pub/2020/circuits/zoom-in</t>
         </is>
       </c>
     </row>
     <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>4. Mechanistic interpretability</t>
         </is>
@@ -1227,62 +1325,72 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>representation engineering; linear probing; concept vector; residual stream; steering; transparency; Llama</t>
+          <t>representation engineering; linear probing; concept vector; residual stream; steering; Llama; transparency</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Shows that high-level concepts (honesty, fairness, emotion) are linearly encoded in LLM residual streams and can be measured and causally manipulated via contrast vectors — the primary methodological toolkit we use.</t>
+          <t>Shows that high-level concepts (honesty, fairness, emotion) are linearly encoded in LLM residual streams and can be causally manipulated via contrast vectors. Primary methodological toolkit for this paper.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Zou, A., Phan, L., Chen, S., Campbell, J., Guo, P., &amp; Steinhardt, J. (2023). arXiv:2310.01405.</t>
+          <t>Zou, A. et al. (2023). arXiv:2310.01405.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2310.01405</t>
         </is>
       </c>
     </row>
     <row r="19" ht="72" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>4. Mechanistic interpretability</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Turner, Mini, MacDiarmid &amp; Rumbelow</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Activation Addition: Steering Language Models Without Optimization</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>arXiv:2308.10248</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>activation addition; steering; residual stream; causal intervention; GPT-2</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Demonstrates that adding a scaled concept direction to GPT-2's residual stream causally shifts model outputs in the predicted direction (e.g., injecting 'banana' direction causes banana-related completions).</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Turner, A., Mini, L., MacDiarmid, J., &amp; Rumbelow, M. (2023). arXiv:2308.10248.</t>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Demonstrates that adding a scaled concept direction to the residual stream causally shifts model outputs in the predicted direction.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Turner, A. et al. (2023). arXiv:2308.10248.</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2308.10248</t>
         </is>
       </c>
     </row>
     <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>4. Mechanistic interpretability</t>
         </is>
@@ -1297,72 +1405,104 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>The Geometry of Concept Space: Empirical Evidence for the Linear Representation Hypothesis</t>
+          <t>Linear Representation Hypothesis and the Geometry of Large Language Models</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>arXiv preprint</t>
+          <t>arXiv:2311.03658</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>linear representation hypothesis; concept geometry; residual stream; LLM; causal inner product</t>
+          <t>linear representation hypothesis; concept geometry; residual stream; LLM</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Provides theoretical unification and strong empirical evidence for the linear representation hypothesis across multiple LLMs, showing concepts are encoded as orthogonal-ish linear directions.</t>
+          <t>Provides theoretical and empirical evidence that concepts are encoded as orthogonal-ish linear directions in LLM representation spaces.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Park, S., Lindsey, J., Heimersheim, S., Henighan, T., &amp; Olah, C. (2024). arXiv preprint.</t>
+          <t>Park, S. et al. (2024). arXiv:2311.03658.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2311.03658</t>
         </is>
       </c>
     </row>
     <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>4. Mechanistic interpretability</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Sofroniew, Lindsey et al.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Emotion Concepts and Their Function in a Large Language Model</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>arXiv:2604.07729</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>emotion; functional emotions; concept vector; residual stream; causal steering; Claude; Anthropic; mechanistic interpretability; alignment</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Builds and validates concept vectors for 171 emotions in Claude Sonnet; the vectors track emotion relevance during conversations and causally shift misaligned behaviors — the direct methodological template for this paper.</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Sofroniew, N., Kauvar, I., Saunders, W., et al. (2026). arXiv:2604.07729.</t>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>emotion; functional emotions; concept vector; residual stream; causal steering; Claude; Anthropic; alignment</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Builds and validates concept vectors for 171 emotions in Claude Sonnet; vectors causally shift misaligned behaviors. Direct methodological template for this paper.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Sofroniew, N., Kauvar, I., Saunders, W. et al. (2026). arXiv:2604.07729.</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.07729</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>